--- a/research/traditional_assets/database/data/nigeria/nigeria_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_computers_peripherals.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-7.272727272727273</v>
+        <v>-40.44444444444444</v>
       </c>
       <c r="H2">
-        <v>-7.272727272727273</v>
+        <v>-40.44444444444444</v>
       </c>
       <c r="I2">
-        <v>-7.581818181818181</v>
+        <v>-52.44444444444444</v>
       </c>
       <c r="J2">
-        <v>-7.581818181818181</v>
+        <v>-52.44444444444444</v>
       </c>
       <c r="K2">
-        <v>-4.71</v>
+        <v>-2.6</v>
       </c>
       <c r="L2">
-        <v>-85.63636363636364</v>
+        <v>-288.8888888888889</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,70 +630,61 @@
         <v>0.076</v>
       </c>
       <c r="V2">
-        <v>0.05314685314685315</v>
+        <v>0.05801526717557252</v>
       </c>
       <c r="W2">
-        <v>0.3437956204379562</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="X2">
-        <v>1.066937524537537</v>
+        <v>1.959555794126074</v>
       </c>
       <c r="Y2">
-        <v>-0.723141904099581</v>
-      </c>
-      <c r="Z2">
-        <v>-0.04486133768352368</v>
-      </c>
-      <c r="AA2">
-        <v>0.340130505709625</v>
+        <v>-1.816698651268931</v>
       </c>
       <c r="AB2">
-        <v>0.1420712359758085</v>
-      </c>
-      <c r="AC2">
-        <v>0.1980592697338165</v>
+        <v>0.2437377334827929</v>
       </c>
       <c r="AD2">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="AG2">
-        <v>15.024</v>
+        <v>15.224</v>
       </c>
       <c r="AH2">
-        <v>0.9134906231094978</v>
+        <v>0.9211318482841663</v>
       </c>
       <c r="AI2">
-        <v>-1.372727272727273</v>
+        <v>-1.0625</v>
       </c>
       <c r="AJ2">
-        <v>0.9130910416919897</v>
+        <v>0.920769323817588</v>
       </c>
       <c r="AK2">
-        <v>-1.356446370530877</v>
+        <v>-1.051671732522796</v>
       </c>
       <c r="AL2">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="AM2">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="AN2">
-        <v>-48.55305466237942</v>
+        <v>-41.35135135135135</v>
       </c>
       <c r="AO2">
-        <v>-0.1212209302325581</v>
+        <v>-0.1991561181434599</v>
       </c>
       <c r="AP2">
-        <v>-48.30868167202572</v>
+        <v>-41.14594594594595</v>
       </c>
       <c r="AQ2">
-        <v>-0.1212209302325581</v>
+        <v>-0.1991561181434599</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-7.272727272727273</v>
+        <v>-40.44444444444444</v>
       </c>
       <c r="H3">
-        <v>-7.272727272727273</v>
+        <v>-40.44444444444444</v>
       </c>
       <c r="I3">
-        <v>-7.581818181818181</v>
+        <v>-52.44444444444444</v>
       </c>
       <c r="J3">
-        <v>-7.581818181818181</v>
+        <v>-52.44444444444444</v>
       </c>
       <c r="K3">
-        <v>-4.71</v>
+        <v>-2.6</v>
       </c>
       <c r="L3">
-        <v>-85.63636363636364</v>
+        <v>-288.8888888888889</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,70 +746,61 @@
         <v>0.076</v>
       </c>
       <c r="V3">
-        <v>0.05314685314685315</v>
+        <v>0.05801526717557252</v>
       </c>
       <c r="W3">
-        <v>0.3437956204379562</v>
+        <v>0.1428571428571429</v>
       </c>
       <c r="X3">
-        <v>1.066937524537537</v>
+        <v>1.959555794126074</v>
       </c>
       <c r="Y3">
-        <v>-0.723141904099581</v>
-      </c>
-      <c r="Z3">
-        <v>-0.04486133768352368</v>
-      </c>
-      <c r="AA3">
-        <v>0.340130505709625</v>
+        <v>-1.816698651268931</v>
       </c>
       <c r="AB3">
-        <v>0.1420712359758085</v>
-      </c>
-      <c r="AC3">
-        <v>0.1980592697338165</v>
+        <v>0.2437377334827929</v>
       </c>
       <c r="AD3">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="AG3">
-        <v>15.024</v>
+        <v>15.224</v>
       </c>
       <c r="AH3">
-        <v>0.9134906231094978</v>
+        <v>0.9211318482841663</v>
       </c>
       <c r="AI3">
-        <v>-1.372727272727273</v>
+        <v>-1.0625</v>
       </c>
       <c r="AJ3">
-        <v>0.9130910416919897</v>
+        <v>0.920769323817588</v>
       </c>
       <c r="AK3">
-        <v>-1.356446370530877</v>
+        <v>-1.051671732522796</v>
       </c>
       <c r="AL3">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="AM3">
-        <v>3.44</v>
+        <v>2.37</v>
       </c>
       <c r="AN3">
-        <v>-48.55305466237942</v>
+        <v>-41.35135135135135</v>
       </c>
       <c r="AO3">
-        <v>-0.1212209302325581</v>
+        <v>-0.1991561181434599</v>
       </c>
       <c r="AP3">
-        <v>-48.30868167202572</v>
+        <v>-41.14594594594595</v>
       </c>
       <c r="AQ3">
-        <v>-0.1212209302325581</v>
+        <v>-0.1991561181434599</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_computers_peripherals.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-40.44444444444444</v>
+        <v>-337</v>
       </c>
       <c r="H2">
-        <v>-40.44444444444444</v>
+        <v>-337</v>
       </c>
       <c r="I2">
-        <v>-52.44444444444444</v>
+        <v>-216</v>
       </c>
       <c r="J2">
-        <v>-52.44444444444444</v>
+        <v>-216</v>
       </c>
       <c r="K2">
-        <v>-2.6</v>
+        <v>-1.78</v>
       </c>
       <c r="L2">
-        <v>-288.8888888888889</v>
+        <v>-1780</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,64 +627,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.076</v>
+        <v>0.058</v>
       </c>
       <c r="V2">
-        <v>0.05801526717557252</v>
+        <v>0.02301587301587302</v>
       </c>
       <c r="W2">
-        <v>0.1428571428571429</v>
+        <v>0.08090909090909092</v>
       </c>
       <c r="X2">
-        <v>1.959555794126074</v>
+        <v>0.7990330687410812</v>
       </c>
       <c r="Y2">
-        <v>-1.816698651268931</v>
+        <v>-0.7181239778319902</v>
       </c>
       <c r="AB2">
-        <v>0.2437377334827929</v>
+        <v>0.2309834576696289</v>
       </c>
       <c r="AD2">
-        <v>15.3</v>
+        <v>10.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.3</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
-        <v>15.224</v>
+        <v>10.442</v>
       </c>
       <c r="AH2">
-        <v>0.9211318482841663</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="AI2">
-        <v>-1.0625</v>
+        <v>-1.567164179104478</v>
       </c>
       <c r="AJ2">
-        <v>0.920769323817588</v>
+        <v>0.8055855577842925</v>
       </c>
       <c r="AK2">
-        <v>-1.051671732522796</v>
+        <v>-1.545131695767979</v>
       </c>
       <c r="AL2">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="AM2">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="AN2">
-        <v>-41.35135135135135</v>
+        <v>-53.2994923857868</v>
       </c>
       <c r="AO2">
-        <v>-0.1991561181434599</v>
+        <v>-0.1255813953488372</v>
       </c>
       <c r="AP2">
-        <v>-41.14594594594595</v>
+        <v>-53.00507614213198</v>
       </c>
       <c r="AQ2">
-        <v>-0.1991561181434599</v>
+        <v>-0.1255813953488372</v>
       </c>
     </row>
     <row r="3">
@@ -704,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-40.44444444444444</v>
+        <v>-337</v>
       </c>
       <c r="H3">
-        <v>-40.44444444444444</v>
+        <v>-337</v>
       </c>
       <c r="I3">
-        <v>-52.44444444444444</v>
+        <v>-216</v>
       </c>
       <c r="J3">
-        <v>-52.44444444444444</v>
+        <v>-216</v>
       </c>
       <c r="K3">
-        <v>-2.6</v>
+        <v>-1.78</v>
       </c>
       <c r="L3">
-        <v>-288.8888888888889</v>
+        <v>-1780</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,64 +743,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.076</v>
+        <v>0.058</v>
       </c>
       <c r="V3">
-        <v>0.05801526717557252</v>
+        <v>0.02301587301587302</v>
       </c>
       <c r="W3">
-        <v>0.1428571428571429</v>
+        <v>0.08090909090909092</v>
       </c>
       <c r="X3">
-        <v>1.959555794126074</v>
+        <v>0.7990330687410812</v>
       </c>
       <c r="Y3">
-        <v>-1.816698651268931</v>
+        <v>-0.7181239778319902</v>
       </c>
       <c r="AB3">
-        <v>0.2437377334827929</v>
+        <v>0.2309834576696289</v>
       </c>
       <c r="AD3">
-        <v>15.3</v>
+        <v>10.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.3</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>15.224</v>
+        <v>10.442</v>
       </c>
       <c r="AH3">
-        <v>0.9211318482841663</v>
+        <v>0.8064516129032259</v>
       </c>
       <c r="AI3">
-        <v>-1.0625</v>
+        <v>-1.567164179104478</v>
       </c>
       <c r="AJ3">
-        <v>0.920769323817588</v>
+        <v>0.8055855577842925</v>
       </c>
       <c r="AK3">
-        <v>-1.051671732522796</v>
+        <v>-1.545131695767979</v>
       </c>
       <c r="AL3">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="AM3">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="AN3">
-        <v>-41.35135135135135</v>
+        <v>-53.2994923857868</v>
       </c>
       <c r="AO3">
-        <v>-0.1991561181434599</v>
+        <v>-0.1255813953488372</v>
       </c>
       <c r="AP3">
-        <v>-41.14594594594595</v>
+        <v>-53.00507614213198</v>
       </c>
       <c r="AQ3">
-        <v>-0.1991561181434599</v>
+        <v>-0.1255813953488372</v>
       </c>
     </row>
   </sheetData>
